--- a/test-harness/.tmp/aggregate-filled.xlsx
+++ b/test-harness/.tmp/aggregate-filled.xlsx
@@ -418,7 +418,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Generated: 2026-04-23T06:51:38.197Z</v>
+        <v>Generated: 2026-04-23T12:37:17.380Z</v>
       </c>
     </row>
     <row r="6">
@@ -844,26 +844,26 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Badjia</v>
+        <v>Kangahun CHC</v>
       </c>
       <c r="B14" t="str">
-        <v>YuQRtpLP10I</v>
+        <v>wUmVUKhnPuy</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Kangahun CHC</v>
+        <v>Koribondo CHC</v>
       </c>
       <c r="B15" t="str">
-        <v>wUmVUKhnPuy</v>
+        <v>mwN7QuEfT8m</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Koribondo CHC</v>
+        <v>Badjia</v>
       </c>
       <c r="B16" t="str">
-        <v>mwN7QuEfT8m</v>
+        <v>YuQRtpLP10I</v>
       </c>
     </row>
     <row r="17">
@@ -916,18 +916,18 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bandaperie CHP</v>
+        <v>Juma MCHP</v>
       </c>
       <c r="B23" t="str">
-        <v>U7yKrx2QVet</v>
+        <v>V6QWyB0KqvP</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Juma MCHP</v>
+        <v>Bandaperie CHP</v>
       </c>
       <c r="B24" t="str">
-        <v>V6QWyB0KqvP</v>
+        <v>U7yKrx2QVet</v>
       </c>
     </row>
     <row r="25">
@@ -1180,18 +1180,18 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Rofutha MCHP</v>
+        <v>Banana Island MCHP</v>
       </c>
       <c r="B56" t="str">
-        <v>G5FuODAbH6X</v>
+        <v>jjtzkzrmG7s</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Banana Island MCHP</v>
+        <v>Rofutha MCHP</v>
       </c>
       <c r="B57" t="str">
-        <v>jjtzkzrmG7s</v>
+        <v>G5FuODAbH6X</v>
       </c>
     </row>
     <row r="58">
@@ -1372,18 +1372,18 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Nekabo CHC</v>
+        <v>Kissy Town CHP</v>
       </c>
       <c r="B80" t="str">
-        <v>L4Tw4NlaMjn</v>
+        <v>lmNWdmeOYmV</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Kissy Town CHP</v>
+        <v>Nekabo CHC</v>
       </c>
       <c r="B81" t="str">
-        <v>lmNWdmeOYmV</v>
+        <v>L4Tw4NlaMjn</v>
       </c>
     </row>
     <row r="82">
@@ -1492,18 +1492,18 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>KingHarman Rd. Hospital</v>
+        <v>Masiaka CHC</v>
       </c>
       <c r="B95" t="str">
-        <v>gei3Sqw8do7</v>
+        <v>EURoFVjowXs</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Masiaka CHC</v>
+        <v>KingHarman Rd. Hospital</v>
       </c>
       <c r="B96" t="str">
-        <v>EURoFVjowXs</v>
+        <v>gei3Sqw8do7</v>
       </c>
     </row>
     <row r="97">
@@ -1612,18 +1612,18 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Stella Maries Clinic</v>
+        <v>Yemoh Town CHC</v>
       </c>
       <c r="B110" t="str">
-        <v>Ea3j0kUvyWg</v>
+        <v>RhJbg8UD75Q</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Yemoh Town CHC</v>
+        <v>Stella Maries Clinic</v>
       </c>
       <c r="B111" t="str">
-        <v>RhJbg8UD75Q</v>
+        <v>Ea3j0kUvyWg</v>
       </c>
     </row>
     <row r="112">
@@ -1932,18 +1932,18 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Marie Stopes (Gbense) Clinic</v>
+        <v>Kokoru CHP</v>
       </c>
       <c r="B150" t="str">
-        <v>Bift1B4gjru</v>
+        <v>F2TAF765q1b</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Kokoru CHP</v>
+        <v>Marie Stopes (Gbense) Clinic</v>
       </c>
       <c r="B151" t="str">
-        <v>F2TAF765q1b</v>
+        <v>Bift1B4gjru</v>
       </c>
     </row>
     <row r="152">
@@ -2060,18 +2060,18 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Hamdalai MCHP</v>
+        <v>Sembehun MCHP</v>
       </c>
       <c r="B166" t="str">
-        <v>HDOnfLXKkYs</v>
+        <v>IWM4eKPJJSc</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Sembehun MCHP</v>
+        <v>Hamdalai MCHP</v>
       </c>
       <c r="B167" t="str">
-        <v>IWM4eKPJJSc</v>
+        <v>HDOnfLXKkYs</v>
       </c>
     </row>
     <row r="168">
@@ -2164,18 +2164,18 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Makona MCHP</v>
+        <v>Bonkababay MCHP</v>
       </c>
       <c r="B179" t="str">
-        <v>JKdMirJ02nv</v>
+        <v>IcVHzEm0b6Z</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Bonkababay MCHP</v>
+        <v>Makona MCHP</v>
       </c>
       <c r="B180" t="str">
-        <v>IcVHzEm0b6Z</v>
+        <v>JKdMirJ02nv</v>
       </c>
     </row>
     <row r="181">
@@ -2284,18 +2284,18 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Binkolo CHC</v>
+        <v>Bucksal Clinic</v>
       </c>
       <c r="B194" t="str">
-        <v>GHHvGp7tgtZ</v>
+        <v>vRC0stJ5y9Q</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Bucksal Clinic</v>
+        <v>Binkolo CHC</v>
       </c>
       <c r="B195" t="str">
-        <v>vRC0stJ5y9Q</v>
+        <v>GHHvGp7tgtZ</v>
       </c>
     </row>
     <row r="196">
@@ -2444,18 +2444,18 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Kindoyal Hospital</v>
+        <v>Mamanso Kafla MCHP</v>
       </c>
       <c r="B214" t="str">
-        <v>uROAmk9ymNE</v>
+        <v>T1lTKu6zkHN</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Mamanso Kafla MCHP</v>
+        <v>Kindoyal Hospital</v>
       </c>
       <c r="B215" t="str">
-        <v>T1lTKu6zkHN</v>
+        <v>uROAmk9ymNE</v>
       </c>
     </row>
     <row r="216">
@@ -2612,18 +2612,18 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Jangalor MCHP</v>
+        <v>Delken MCHP</v>
       </c>
       <c r="B235" t="str">
-        <v>qzm5ww3U0vz</v>
+        <v>sSgOnY1Xqd9</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Delken MCHP</v>
+        <v>Jangalor MCHP</v>
       </c>
       <c r="B236" t="str">
-        <v>sSgOnY1Xqd9</v>
+        <v>qzm5ww3U0vz</v>
       </c>
     </row>
     <row r="237">
@@ -2852,18 +2852,18 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Tikonko CHC</v>
+        <v>Senehun Gbloh MCHP</v>
       </c>
       <c r="B265" t="str">
-        <v>KYXbIQBQgP1</v>
+        <v>Efmr3Xo36DR</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Senehun Gbloh MCHP</v>
+        <v>Tikonko CHC</v>
       </c>
       <c r="B266" t="str">
-        <v>Efmr3Xo36DR</v>
+        <v>KYXbIQBQgP1</v>
       </c>
     </row>
     <row r="267">
@@ -2900,18 +2900,18 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Dulukoro MCHP</v>
+        <v>Gibena MCHP</v>
       </c>
       <c r="B271" t="str">
-        <v>RpjUEvgWSNO</v>
+        <v>ywNG86IY4Ve</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Gibena MCHP</v>
+        <v>Dulukoro MCHP</v>
       </c>
       <c r="B272" t="str">
-        <v>ywNG86IY4Ve</v>
+        <v>RpjUEvgWSNO</v>
       </c>
     </row>
     <row r="273">
@@ -2956,26 +2956,26 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Njagbahun (L.Banta) MCHP</v>
+        <v>Numea CHC</v>
       </c>
       <c r="B278" t="str">
-        <v>u3B5RqJuDAP</v>
+        <v>PduUQmdt0pB</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Numea CHC</v>
+        <v>Tongoro MCHP</v>
       </c>
       <c r="B279" t="str">
-        <v>PduUQmdt0pB</v>
+        <v>iIpPPnnzDo6</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Tongoro MCHP</v>
+        <v>Njagbahun (L.Banta) MCHP</v>
       </c>
       <c r="B280" t="str">
-        <v>iIpPPnnzDo6</v>
+        <v>u3B5RqJuDAP</v>
       </c>
     </row>
     <row r="281">
@@ -2988,18 +2988,18 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Dalakuru CHP</v>
+        <v>Macrogba MCHP</v>
       </c>
       <c r="B282" t="str">
-        <v>Xytauldn2QJ</v>
+        <v>Xnif5imKLlT</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Macrogba MCHP</v>
+        <v>Dalakuru CHP</v>
       </c>
       <c r="B283" t="str">
-        <v>Xnif5imKLlT</v>
+        <v>Xytauldn2QJ</v>
       </c>
     </row>
     <row r="284">
@@ -3020,18 +3020,18 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>New London MCHP</v>
+        <v>Gbamgbama CHC</v>
       </c>
       <c r="B286" t="str">
-        <v>uczMdDZXdtl</v>
+        <v>D2rB1GRuh8C</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Gbamgbama CHC</v>
+        <v>New London MCHP</v>
       </c>
       <c r="B287" t="str">
-        <v>D2rB1GRuh8C</v>
+        <v>uczMdDZXdtl</v>
       </c>
     </row>
     <row r="288">
@@ -3292,18 +3292,18 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Damballa CHC</v>
+        <v>Tihun CHC</v>
       </c>
       <c r="B320" t="str">
-        <v>wByqtWCCuDJ</v>
+        <v>ua5GXy2uhBR</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Tihun CHC</v>
+        <v>Damballa CHC</v>
       </c>
       <c r="B321" t="str">
-        <v>ua5GXy2uhBR</v>
+        <v>wByqtWCCuDJ</v>
       </c>
     </row>
     <row r="322">
@@ -3404,18 +3404,18 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Kumala CHP</v>
+        <v>Kunsho CHP</v>
       </c>
       <c r="B334" t="str">
-        <v>CvYsZipdHMN</v>
+        <v>tdhB1JXYBx2</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Kunsho CHP</v>
+        <v>Kumala CHP</v>
       </c>
       <c r="B335" t="str">
-        <v>tdhB1JXYBx2</v>
+        <v>CvYsZipdHMN</v>
       </c>
     </row>
     <row r="336">
@@ -3492,18 +3492,18 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Gbaneh Lol MCHP</v>
+        <v>Makama MCHP</v>
       </c>
       <c r="B345" t="str">
-        <v>oxAoPoePpqy</v>
+        <v>Dbn6fyCgMBV</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Makama MCHP</v>
+        <v>Gbaneh Lol MCHP</v>
       </c>
       <c r="B346" t="str">
-        <v>Dbn6fyCgMBV</v>
+        <v>oxAoPoePpqy</v>
       </c>
     </row>
     <row r="347">
@@ -3516,18 +3516,18 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Gbetema MCHP (Fiama)</v>
+        <v>Masamboi MCHP</v>
       </c>
       <c r="B348" t="str">
-        <v>as1dnmlXLzG</v>
+        <v>Hu31NCRjZlj</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Masamboi MCHP</v>
+        <v>Gbetema MCHP (Fiama)</v>
       </c>
       <c r="B349" t="str">
-        <v>Hu31NCRjZlj</v>
+        <v>as1dnmlXLzG</v>
       </c>
     </row>
     <row r="350">
@@ -3540,18 +3540,18 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Rotaimbana MCHP</v>
+        <v>Tengbewabu MCHP</v>
       </c>
       <c r="B351" t="str">
-        <v>GMOl74xzmAE</v>
+        <v>gfWvbbgdjoS</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tengbewabu MCHP</v>
+        <v>Rotaimbana MCHP</v>
       </c>
       <c r="B352" t="str">
-        <v>gfWvbbgdjoS</v>
+        <v>GMOl74xzmAE</v>
       </c>
     </row>
     <row r="353">
@@ -3564,18 +3564,18 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Sierra Rutile Clinic</v>
+        <v>Koidu Under Five Clinic</v>
       </c>
       <c r="B354" t="str">
-        <v>Bq5nb7UAEGd</v>
+        <v>Ls2ESQONh9S</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Koidu Under Five Clinic</v>
+        <v>Sierra Rutile Clinic</v>
       </c>
       <c r="B355" t="str">
-        <v>Ls2ESQONh9S</v>
+        <v>Bq5nb7UAEGd</v>
       </c>
     </row>
     <row r="356">
@@ -3676,34 +3676,34 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Bassia MCHP</v>
+        <v>Masumana MCHP</v>
       </c>
       <c r="B368" t="str">
-        <v>tlvNeDXXrS7</v>
+        <v>UlgEReuUPM4</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Masumana MCHP</v>
+        <v>Bassia MCHP</v>
       </c>
       <c r="B369" t="str">
-        <v>UlgEReuUPM4</v>
+        <v>tlvNeDXXrS7</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Samaia MCHP</v>
+        <v>Gorahun CHC</v>
       </c>
       <c r="B370" t="str">
-        <v>fNL2oehab2Q</v>
+        <v>QpRIPul20Sb</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Gorahun CHC</v>
+        <v>Samaia MCHP</v>
       </c>
       <c r="B371" t="str">
-        <v>QpRIPul20Sb</v>
+        <v>fNL2oehab2Q</v>
       </c>
     </row>
     <row r="372">
@@ -3900,18 +3900,18 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Bauya (Kongbora) CHC</v>
+        <v>Foindu (Lower Bamabara) CHC</v>
       </c>
       <c r="B396" t="str">
-        <v>iMZihUMzH92</v>
+        <v>pNPmNeqyrim</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Foindu (Lower Bamabara) CHC</v>
+        <v>Bauya (Kongbora) CHC</v>
       </c>
       <c r="B397" t="str">
-        <v>pNPmNeqyrim</v>
+        <v>iMZihUMzH92</v>
       </c>
     </row>
     <row r="398">
@@ -4044,18 +4044,18 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Pelewahun MCHP</v>
+        <v>Rosengbeh MCHP</v>
       </c>
       <c r="B414" t="str">
-        <v>MQHszd6K6V5</v>
+        <v>x3ti3t9eOuX</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Rosengbeh MCHP</v>
+        <v>Pelewahun MCHP</v>
       </c>
       <c r="B415" t="str">
-        <v>x3ti3t9eOuX</v>
+        <v>MQHszd6K6V5</v>
       </c>
     </row>
     <row r="416">
@@ -4068,34 +4068,34 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Rapha Clinic</v>
+        <v>PMO Clinetown</v>
       </c>
       <c r="B417" t="str">
-        <v>is3w3HROKVc</v>
+        <v>g7BLyiBb0ET</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>PMO Clinetown</v>
+        <v>Rapha Clinic</v>
       </c>
       <c r="B418" t="str">
-        <v>g7BLyiBb0ET</v>
+        <v>is3w3HROKVc</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Koya MCHP</v>
+        <v>Karina MCHP</v>
       </c>
       <c r="B419" t="str">
-        <v>brnL0W3Fbsj</v>
+        <v>ObV5AR1NECl</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Karina MCHP</v>
+        <v>Koya MCHP</v>
       </c>
       <c r="B420" t="str">
-        <v>ObV5AR1NECl</v>
+        <v>brnL0W3Fbsj</v>
       </c>
     </row>
     <row r="421">
@@ -4236,18 +4236,18 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Ngiehun CHC</v>
+        <v>Moyiba CHC</v>
       </c>
       <c r="B438" t="str">
-        <v>sznCEDMABa2</v>
+        <v>zEsMdeJOty4</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Moyiba CHC</v>
+        <v>Ngiehun CHC</v>
       </c>
       <c r="B439" t="str">
-        <v>zEsMdeJOty4</v>
+        <v>sznCEDMABa2</v>
       </c>
     </row>
     <row r="440">
@@ -4356,18 +4356,18 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Ngueh MCHP</v>
+        <v>Kpetema MCHP</v>
       </c>
       <c r="B453" t="str">
-        <v>Vw4Uv6UPIPC</v>
+        <v>kDxbU1uSBFh</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Kpetema MCHP</v>
+        <v>Ngueh MCHP</v>
       </c>
       <c r="B454" t="str">
-        <v>kDxbU1uSBFh</v>
+        <v>Vw4Uv6UPIPC</v>
       </c>
     </row>
     <row r="455">
@@ -4532,18 +4532,18 @@
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Handicap Clinic</v>
+        <v>Modonkor CHP</v>
       </c>
       <c r="B475" t="str">
-        <v>DSBXsRQSXUW</v>
+        <v>cXMQtUId06K</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Modonkor CHP</v>
+        <v>Handicap Clinic</v>
       </c>
       <c r="B476" t="str">
-        <v>cXMQtUId06K</v>
+        <v>DSBXsRQSXUW</v>
       </c>
     </row>
     <row r="477">
@@ -4604,18 +4604,18 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Pellie CHC</v>
+        <v>Semabu MCHP</v>
       </c>
       <c r="B484" t="str">
-        <v>HQoxFu4lYPS</v>
+        <v>Dluer5aKZmd</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Semabu MCHP</v>
+        <v>Pellie CHC</v>
       </c>
       <c r="B485" t="str">
-        <v>Dluer5aKZmd</v>
+        <v>HQoxFu4lYPS</v>
       </c>
     </row>
     <row r="486">
@@ -4804,18 +4804,18 @@
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Sahn Bumpe MCHP</v>
+        <v>Rosint Buya MCHP</v>
       </c>
       <c r="B509" t="str">
-        <v>NDqR2cWlVy3</v>
+        <v>el8sgzyHuEe</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Rosint Buya MCHP</v>
+        <v>Sahn Bumpe MCHP</v>
       </c>
       <c r="B510" t="str">
-        <v>el8sgzyHuEe</v>
+        <v>NDqR2cWlVy3</v>
       </c>
     </row>
     <row r="511">
@@ -5228,10 +5228,10 @@
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Koije MCHP</v>
+        <v>Kawaya MCHP</v>
       </c>
       <c r="B562" t="str">
-        <v>vj0HUVazItT</v>
+        <v>qMbxFg9McOF</v>
       </c>
     </row>
     <row r="563">
@@ -5244,10 +5244,10 @@
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Kawaya MCHP</v>
+        <v>Koije MCHP</v>
       </c>
       <c r="B564" t="str">
-        <v>qMbxFg9McOF</v>
+        <v>vj0HUVazItT</v>
       </c>
     </row>
     <row r="565">
@@ -5332,18 +5332,18 @@
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Jui CHP</v>
+        <v>Bumpe CHC</v>
       </c>
       <c r="B575" t="str">
-        <v>VH8vOjm0l8w</v>
+        <v>E497Rk80ivZ</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Bumpe CHC</v>
+        <v>Jui CHP</v>
       </c>
       <c r="B576" t="str">
-        <v>E497Rk80ivZ</v>
+        <v>VH8vOjm0l8w</v>
       </c>
     </row>
     <row r="577">
@@ -5380,18 +5380,18 @@
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Mamusa MCHP</v>
+        <v>Baiama CHP</v>
       </c>
       <c r="B581" t="str">
-        <v>FRX63UWciyO</v>
+        <v>XtuhRhmbrJM</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Baiama CHP</v>
+        <v>Mamusa MCHP</v>
       </c>
       <c r="B582" t="str">
-        <v>XtuhRhmbrJM</v>
+        <v>FRX63UWciyO</v>
       </c>
     </row>
     <row r="583">
@@ -5404,26 +5404,26 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>kamba mamudia</v>
+        <v>Madina (BUM) CHC</v>
       </c>
       <c r="B584" t="str">
-        <v>zO5hgxxfU4T</v>
+        <v>gE3gEGZbQMi</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Family Clinic</v>
+        <v>kamba mamudia</v>
       </c>
       <c r="B585" t="str">
-        <v>fXT1scbEObM</v>
+        <v>zO5hgxxfU4T</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Madina (BUM) CHC</v>
+        <v>Family Clinic</v>
       </c>
       <c r="B586" t="str">
-        <v>gE3gEGZbQMi</v>
+        <v>fXT1scbEObM</v>
       </c>
     </row>
     <row r="587">
@@ -5492,18 +5492,18 @@
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Mamalikie MCHP</v>
+        <v>Govt. Hospital Moyamba</v>
       </c>
       <c r="B595" t="str">
-        <v>ALZ2qr5u0X0</v>
+        <v>U8uqyDAu5bH</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Govt. Hospital Moyamba</v>
+        <v>Mamalikie MCHP</v>
       </c>
       <c r="B596" t="str">
-        <v>U8uqyDAu5bH</v>
+        <v>ALZ2qr5u0X0</v>
       </c>
     </row>
     <row r="597">
@@ -5860,18 +5860,18 @@
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Kamba MCHP</v>
+        <v>Bendu Mameima CHC</v>
       </c>
       <c r="B641" t="str">
-        <v>cJ7omISg7gG</v>
+        <v>amgb83zVxp5</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Bendu Mameima CHC</v>
+        <v>Kamba MCHP</v>
       </c>
       <c r="B642" t="str">
-        <v>amgb83zVxp5</v>
+        <v>cJ7omISg7gG</v>
       </c>
     </row>
     <row r="643">
@@ -5996,34 +5996,34 @@
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Griema MCHP</v>
+        <v>Torma Bum CHP</v>
       </c>
       <c r="B658" t="str">
-        <v>KR0jLuFOB3d</v>
+        <v>rZkUcho9Z65</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Torma Bum CHP</v>
+        <v>Griema MCHP</v>
       </c>
       <c r="B659" t="str">
-        <v>rZkUcho9Z65</v>
+        <v>KR0jLuFOB3d</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Calaba town CHC</v>
+        <v>Rokel (Masimera) MCHP</v>
       </c>
       <c r="B660" t="str">
-        <v>KiheEgvUZ0i</v>
+        <v>UUZoBCSn245</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Rokel (Masimera) MCHP</v>
+        <v>Calaba town CHC</v>
       </c>
       <c r="B661" t="str">
-        <v>UUZoBCSn245</v>
+        <v>KiheEgvUZ0i</v>
       </c>
     </row>
     <row r="662">
@@ -6244,18 +6244,18 @@
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Burma 2 MCHP</v>
+        <v>Mbokie CHP</v>
       </c>
       <c r="B689" t="str">
-        <v>qvHMAxtWWK6</v>
+        <v>nImgPWDVQIa</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Mbokie CHP</v>
+        <v>Burma 2 MCHP</v>
       </c>
       <c r="B690" t="str">
-        <v>nImgPWDVQIa</v>
+        <v>qvHMAxtWWK6</v>
       </c>
     </row>
     <row r="691">
@@ -6444,18 +6444,18 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>Ganya MCHP</v>
+        <v>Kabba Ferry MCHP</v>
       </c>
       <c r="B714" t="str">
-        <v>JttXgTlQAGE</v>
+        <v>TWMVxJANJeU</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>Kabba Ferry MCHP</v>
+        <v>Ganya MCHP</v>
       </c>
       <c r="B715" t="str">
-        <v>TWMVxJANJeU</v>
+        <v>JttXgTlQAGE</v>
       </c>
     </row>
     <row r="716">
@@ -6684,18 +6684,18 @@
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>Sumbuya CHC</v>
+        <v>Koakor MCHP</v>
       </c>
       <c r="B744" t="str">
-        <v>W2KnxOMvmgE</v>
+        <v>EQc3n1juPFn</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>Koakor MCHP</v>
+        <v>Sumbuya CHC</v>
       </c>
       <c r="B745" t="str">
-        <v>EQc3n1juPFn</v>
+        <v>W2KnxOMvmgE</v>
       </c>
     </row>
     <row r="746">
@@ -6876,18 +6876,18 @@
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>Hima MCHP</v>
+        <v>Kuranko MCHP</v>
       </c>
       <c r="B768" t="str">
-        <v>l2kZRcJjomr</v>
+        <v>WUQrS4Yqmoy</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>Kuranko MCHP</v>
+        <v>Hima MCHP</v>
       </c>
       <c r="B769" t="str">
-        <v>WUQrS4Yqmoy</v>
+        <v>l2kZRcJjomr</v>
       </c>
     </row>
     <row r="770">
@@ -6980,18 +6980,18 @@
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>SL Red Cross (BMC) Clinic</v>
+        <v>Manewa MCHP</v>
       </c>
       <c r="B781" t="str">
-        <v>nCh5dBoJVNw</v>
+        <v>CTnuuI55SOj</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>Manewa MCHP</v>
+        <v>SL Red Cross (BMC) Clinic</v>
       </c>
       <c r="B782" t="str">
-        <v>CTnuuI55SOj</v>
+        <v>nCh5dBoJVNw</v>
       </c>
     </row>
     <row r="783">
@@ -7028,18 +7028,18 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>Masongbo Limba MCHP</v>
+        <v>Jembe CHC</v>
       </c>
       <c r="B787" t="str">
-        <v>PhR1PdMTzhW</v>
+        <v>Umh4HKqqFp6</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>Jembe CHC</v>
+        <v>Masongbo Limba MCHP</v>
       </c>
       <c r="B788" t="str">
-        <v>Umh4HKqqFp6</v>
+        <v>PhR1PdMTzhW</v>
       </c>
     </row>
     <row r="789">
@@ -7116,18 +7116,18 @@
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>Kagbulor CHP</v>
+        <v>Karlu CHC</v>
       </c>
       <c r="B798" t="str">
-        <v>n3MRjKtwr3O</v>
+        <v>K00jR5dmoFZ</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>Karlu CHC</v>
+        <v>Kagbulor CHP</v>
       </c>
       <c r="B799" t="str">
-        <v>K00jR5dmoFZ</v>
+        <v>n3MRjKtwr3O</v>
       </c>
     </row>
     <row r="800">
@@ -7684,18 +7684,18 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>Bongor MCHP</v>
+        <v>Njama MCHP</v>
       </c>
       <c r="B869" t="str">
-        <v>zAyK28LLaez</v>
+        <v>WMj6mBDw76A</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>Njama MCHP</v>
+        <v>Bongor MCHP</v>
       </c>
       <c r="B870" t="str">
-        <v>WMj6mBDw76A</v>
+        <v>zAyK28LLaez</v>
       </c>
     </row>
     <row r="871">
@@ -7804,18 +7804,18 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>Sandayeima MCHP</v>
+        <v>Kambama CHP</v>
       </c>
       <c r="B884" t="str">
-        <v>oUR5HPmim7E</v>
+        <v>mYMJHVqdBKt</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>Kambama CHP</v>
+        <v>Sandayeima MCHP</v>
       </c>
       <c r="B885" t="str">
-        <v>mYMJHVqdBKt</v>
+        <v>oUR5HPmim7E</v>
       </c>
     </row>
     <row r="886">
@@ -7836,26 +7836,26 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>Kagbasia MCHP</v>
+        <v>Waiima (Kori) MCHP</v>
       </c>
       <c r="B888" t="str">
-        <v>T3iVyvrCpZ0</v>
+        <v>DlLBIHdpaTy</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>Waiima (Kori) MCHP</v>
+        <v>Fobu MCHP</v>
       </c>
       <c r="B889" t="str">
-        <v>DlLBIHdpaTy</v>
+        <v>e0RGds86ow6</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>Fobu MCHP</v>
+        <v>Kagbasia MCHP</v>
       </c>
       <c r="B890" t="str">
-        <v>e0RGds86ow6</v>
+        <v>T3iVyvrCpZ0</v>
       </c>
     </row>
     <row r="891">
@@ -8004,18 +8004,18 @@
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>Sengema (Luawa) CHP</v>
+        <v>Bambara Kaima CHP</v>
       </c>
       <c r="B909" t="str">
-        <v>wkYbuEwNWyf</v>
+        <v>LOpWauwwghf</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>Bambara Kaima CHP</v>
+        <v>Sengema (Luawa) CHP</v>
       </c>
       <c r="B910" t="str">
-        <v>LOpWauwwghf</v>
+        <v>wkYbuEwNWyf</v>
       </c>
     </row>
     <row r="911">
@@ -8076,18 +8076,18 @@
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>Sierra Leone</v>
+        <v>Koyagbema MCHP</v>
       </c>
       <c r="B918" t="str">
-        <v>ImspTQPwCqd</v>
+        <v>Kmu7ox2MiiU</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>Koyagbema MCHP</v>
+        <v>Sierra Leone</v>
       </c>
       <c r="B919" t="str">
-        <v>Kmu7ox2MiiU</v>
+        <v>ImspTQPwCqd</v>
       </c>
     </row>
     <row r="920">
@@ -8132,34 +8132,34 @@
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>Blama CHC</v>
+        <v>Koardu MCHP</v>
       </c>
       <c r="B925" t="str">
-        <v>kUzpbgPCwVA</v>
+        <v>PwoQgMJNWbR</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>Koardu MCHP</v>
+        <v>Blama CHC</v>
       </c>
       <c r="B926" t="str">
-        <v>PwoQgMJNWbR</v>
+        <v>kUzpbgPCwVA</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>Mange Bissan MCHP</v>
+        <v>Bumbanday MCHP</v>
       </c>
       <c r="B927" t="str">
-        <v>cKXicCOquXe</v>
+        <v>LZclRdyVk1t</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>Bumbanday MCHP</v>
+        <v>Mange Bissan MCHP</v>
       </c>
       <c r="B928" t="str">
-        <v>LZclRdyVk1t</v>
+        <v>cKXicCOquXe</v>
       </c>
     </row>
     <row r="929">
@@ -8260,18 +8260,18 @@
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>Lumley Hospital</v>
+        <v>Liya MCHP</v>
       </c>
       <c r="B941" t="str">
-        <v>PqlNXedmh7u</v>
+        <v>tBRDdxfKbMx</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>Liya MCHP</v>
+        <v>Lumley Hospital</v>
       </c>
       <c r="B942" t="str">
-        <v>tBRDdxfKbMx</v>
+        <v>PqlNXedmh7u</v>
       </c>
     </row>
     <row r="943">
@@ -8292,18 +8292,18 @@
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>Masseseh MCHP</v>
+        <v>Bangambaya MCHP</v>
       </c>
       <c r="B945" t="str">
-        <v>jIrb5XckcU6</v>
+        <v>xQIU41mR69s</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>Bangambaya MCHP</v>
+        <v>Masseseh MCHP</v>
       </c>
       <c r="B946" t="str">
-        <v>xQIU41mR69s</v>
+        <v>jIrb5XckcU6</v>
       </c>
     </row>
     <row r="947">
@@ -8412,34 +8412,34 @@
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>Holy Mary Hospital</v>
+        <v>Ola During Clinic</v>
       </c>
       <c r="B960" t="str">
-        <v>jk1TtiBM5hz</v>
+        <v>tHUYjt9cU6h</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>Ola During Clinic</v>
+        <v>Holy Mary Hospital</v>
       </c>
       <c r="B961" t="str">
-        <v>tHUYjt9cU6h</v>
+        <v>jk1TtiBM5hz</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>Fogbo CHP</v>
+        <v>Foya CHP</v>
       </c>
       <c r="B962" t="str">
-        <v>fGp4OcovQpa</v>
+        <v>qqF8jshIs66</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>Foya CHP</v>
+        <v>Fogbo CHP</v>
       </c>
       <c r="B963" t="str">
-        <v>qqF8jshIs66</v>
+        <v>fGp4OcovQpa</v>
       </c>
     </row>
     <row r="964">
@@ -8556,18 +8556,18 @@
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>Bo</v>
+        <v>Benkia MCHP</v>
       </c>
       <c r="B978" t="str">
-        <v>O6uvpzGd5pu</v>
+        <v>OcRCVRy2M7X</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>Benkia MCHP</v>
+        <v>Bo</v>
       </c>
       <c r="B979" t="str">
-        <v>OcRCVRy2M7X</v>
+        <v>O6uvpzGd5pu</v>
       </c>
     </row>
     <row r="980">
@@ -8612,18 +8612,18 @@
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>Mabang MCHP</v>
+        <v>Gloucester CHP</v>
       </c>
       <c r="B985" t="str">
-        <v>fCFdj2T0Bq1</v>
+        <v>HTDuY3uxj6u</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>Gloucester CHP</v>
+        <v>Mabang MCHP</v>
       </c>
       <c r="B986" t="str">
-        <v>HTDuY3uxj6u</v>
+        <v>fCFdj2T0Bq1</v>
       </c>
     </row>
     <row r="987">
@@ -8676,18 +8676,18 @@
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>Junctionla MCHP</v>
+        <v>Malama MCHP</v>
       </c>
       <c r="B993" t="str">
-        <v>QCnJDmNjQy0</v>
+        <v>kBrq7i12aan</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>Malama MCHP</v>
+        <v>Junctionla MCHP</v>
       </c>
       <c r="B994" t="str">
-        <v>kBrq7i12aan</v>
+        <v>QCnJDmNjQy0</v>
       </c>
     </row>
     <row r="995">
@@ -8788,7 +8788,7 @@
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>Panderu MCHP</v>
+        <v xml:space="preserve"> Panderu MCHP</v>
       </c>
       <c r="B1007" t="str">
         <v>ueuQlqb8ccl</v>
@@ -8820,18 +8820,18 @@
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>Moyeamoh CHP</v>
+        <v>Bambara MCHP</v>
       </c>
       <c r="B1011" t="str">
-        <v>WhCQNekdIwM</v>
+        <v>mUuCjQWMaOc</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>Bambara MCHP</v>
+        <v>Moyeamoh CHP</v>
       </c>
       <c r="B1012" t="str">
-        <v>mUuCjQWMaOc</v>
+        <v>WhCQNekdIwM</v>
       </c>
     </row>
     <row r="1013">
@@ -8972,18 +8972,18 @@
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>Kasanikoro MCHP</v>
+        <v>Baama CHC</v>
       </c>
       <c r="B1030" t="str">
-        <v>jj1MhWhHqta</v>
+        <v>r5WWF9WDzoa</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>Baama CHC</v>
+        <v>Kasanikoro MCHP</v>
       </c>
       <c r="B1031" t="str">
-        <v>r5WWF9WDzoa</v>
+        <v>jj1MhWhHqta</v>
       </c>
     </row>
     <row r="1032">
@@ -9060,18 +9060,18 @@
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>Kagbanthama CHP</v>
+        <v>Mosanda CHP</v>
       </c>
       <c r="B1041" t="str">
-        <v>ZZmMpGIE7pD</v>
+        <v>cDRQOxX1wHO</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>Mosanda CHP</v>
+        <v>Kagbanthama CHP</v>
       </c>
       <c r="B1042" t="str">
-        <v>cDRQOxX1wHO</v>
+        <v>ZZmMpGIE7pD</v>
       </c>
     </row>
     <row r="1043">
@@ -9252,18 +9252,18 @@
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>Mbundorbu MCHP</v>
+        <v>Kagbo MCHP</v>
       </c>
       <c r="B1065" t="str">
-        <v>EuoA3Crpqts</v>
+        <v>OTlKtnhvEm1</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>Kagbo MCHP</v>
+        <v>Mbundorbu MCHP</v>
       </c>
       <c r="B1066" t="str">
-        <v>OTlKtnhvEm1</v>
+        <v>EuoA3Crpqts</v>
       </c>
     </row>
     <row r="1067">
@@ -9380,18 +9380,18 @@
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>Ferry CHP</v>
+        <v>Mutual Faith Clinic</v>
       </c>
       <c r="B1081" t="str">
-        <v>Eyqyhztf8G1</v>
+        <v>Uo4cyJwAhTW</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>Mutual Faith Clinic</v>
+        <v>Ferry CHP</v>
       </c>
       <c r="B1082" t="str">
-        <v>Uo4cyJwAhTW</v>
+        <v>Eyqyhztf8G1</v>
       </c>
     </row>
     <row r="1083">
@@ -9444,18 +9444,18 @@
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>Katick MCHP</v>
+        <v>EDC Unit CHP</v>
       </c>
       <c r="B1089" t="str">
-        <v>Zp2Yi4j2AAH</v>
+        <v>K3k64jslIlL</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>EDC Unit CHP</v>
+        <v>Katick MCHP</v>
       </c>
       <c r="B1090" t="str">
-        <v>K3k64jslIlL</v>
+        <v>Zp2Yi4j2AAH</v>
       </c>
     </row>
     <row r="1091">
@@ -9596,18 +9596,18 @@
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>Wullah Thenkle MCHP</v>
+        <v>Kpewama MCHP</v>
       </c>
       <c r="B1108" t="str">
-        <v>IN2dOk0gY1G</v>
+        <v>DcmSvQd5N8c</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>Kpewama MCHP</v>
+        <v>Wullah Thenkle MCHP</v>
       </c>
       <c r="B1109" t="str">
-        <v>DcmSvQd5N8c</v>
+        <v>IN2dOk0gY1G</v>
       </c>
     </row>
     <row r="1110">
@@ -9644,18 +9644,18 @@
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>Tagrin CHC</v>
+        <v>Bumban MCHP</v>
       </c>
       <c r="B1114" t="str">
-        <v>O63vIA5MVn6</v>
+        <v>OI0BQUurVFS</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>Bumban MCHP</v>
+        <v>Tagrin CHC</v>
       </c>
       <c r="B1115" t="str">
-        <v>OI0BQUurVFS</v>
+        <v>O63vIA5MVn6</v>
       </c>
     </row>
     <row r="1116">
@@ -10012,18 +10012,18 @@
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>Kombilie MCHP</v>
+        <v>Magbeni MCHP</v>
       </c>
       <c r="B1160" t="str">
-        <v>HC2NlwpoXfb</v>
+        <v>UJ80rknbJtm</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>Magbeni MCHP</v>
+        <v>Kombilie MCHP</v>
       </c>
       <c r="B1161" t="str">
-        <v>UJ80rknbJtm</v>
+        <v>HC2NlwpoXfb</v>
       </c>
     </row>
     <row r="1162">

--- a/test-harness/.tmp/aggregate-filled.xlsx
+++ b/test-harness/.tmp/aggregate-filled.xlsx
@@ -418,7 +418,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Generated: 2026-04-23T12:37:17.380Z</v>
+        <v>Generated: 2026-04-23T13:18:37.556Z</v>
       </c>
     </row>
     <row r="6">
@@ -1372,18 +1372,18 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kissy Town CHP</v>
+        <v>Nekabo CHC</v>
       </c>
       <c r="B80" t="str">
-        <v>lmNWdmeOYmV</v>
+        <v>L4Tw4NlaMjn</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Nekabo CHC</v>
+        <v>Kissy Town CHP</v>
       </c>
       <c r="B81" t="str">
-        <v>L4Tw4NlaMjn</v>
+        <v>lmNWdmeOYmV</v>
       </c>
     </row>
     <row r="82">
@@ -1612,18 +1612,18 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Yemoh Town CHC</v>
+        <v>Stella Maries Clinic</v>
       </c>
       <c r="B110" t="str">
-        <v>RhJbg8UD75Q</v>
+        <v>Ea3j0kUvyWg</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Stella Maries Clinic</v>
+        <v>Yemoh Town CHC</v>
       </c>
       <c r="B111" t="str">
-        <v>Ea3j0kUvyWg</v>
+        <v>RhJbg8UD75Q</v>
       </c>
     </row>
     <row r="112">
@@ -1796,18 +1796,18 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Woyama MCHP</v>
+        <v>Kaponkie MCHP</v>
       </c>
       <c r="B133" t="str">
-        <v>fPe1l06MurL</v>
+        <v>Crgx572DnXR</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Kaponkie MCHP</v>
+        <v>Woyama MCHP</v>
       </c>
       <c r="B134" t="str">
-        <v>Crgx572DnXR</v>
+        <v>fPe1l06MurL</v>
       </c>
     </row>
     <row r="135">
@@ -1852,18 +1852,18 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Small Sefadu MCHP</v>
+        <v>Masankoro MCHP</v>
       </c>
       <c r="B140" t="str">
-        <v>ncGs9vXS36w</v>
+        <v>l3jnkNNpoD8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Masankoro MCHP</v>
+        <v>Small Sefadu MCHP</v>
       </c>
       <c r="B141" t="str">
-        <v>l3jnkNNpoD8</v>
+        <v>ncGs9vXS36w</v>
       </c>
     </row>
     <row r="142">
@@ -2532,18 +2532,18 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Magbassabana MCHP</v>
+        <v>Bumpeh River CHP</v>
       </c>
       <c r="B225" t="str">
-        <v>bf6PXrSNMKK</v>
+        <v>mkIugjeYSjE</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Bumpeh River CHP</v>
+        <v>Magbassabana MCHP</v>
       </c>
       <c r="B226" t="str">
-        <v>mkIugjeYSjE</v>
+        <v>bf6PXrSNMKK</v>
       </c>
     </row>
     <row r="227">
@@ -3172,18 +3172,18 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Fatibra CHP</v>
+        <v>Mercy Ship ACFC</v>
       </c>
       <c r="B305" t="str">
-        <v>jfV49JGnYKF</v>
+        <v>xO9WbCvFq5k</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Mercy Ship ACFC</v>
+        <v>Fatibra CHP</v>
       </c>
       <c r="B306" t="str">
-        <v>xO9WbCvFq5k</v>
+        <v>jfV49JGnYKF</v>
       </c>
     </row>
     <row r="307">
@@ -3444,18 +3444,18 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Dankawalie MCHP</v>
+        <v>Mabayo MCHP</v>
       </c>
       <c r="B339" t="str">
-        <v>DErmFP7bri7</v>
+        <v>Xzxy8NuVsLp</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Mabayo MCHP</v>
+        <v>Dankawalie MCHP</v>
       </c>
       <c r="B340" t="str">
-        <v>Xzxy8NuVsLp</v>
+        <v>DErmFP7bri7</v>
       </c>
     </row>
     <row r="341">
@@ -3556,18 +3556,18 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Hill Station MCHP</v>
+        <v>Koidu Under Five Clinic</v>
       </c>
       <c r="B353" t="str">
-        <v>AKvgfYx5WZq</v>
+        <v>Ls2ESQONh9S</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Koidu Under Five Clinic</v>
+        <v>Hill Station MCHP</v>
       </c>
       <c r="B354" t="str">
-        <v>Ls2ESQONh9S</v>
+        <v>AKvgfYx5WZq</v>
       </c>
     </row>
     <row r="355">
@@ -3756,18 +3756,18 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Saahun (kpaka) MCHP</v>
+        <v>Gbonkonka CHP</v>
       </c>
       <c r="B378" t="str">
-        <v>BG2fC2mRFOL</v>
+        <v>v2vi8UaIYlo</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Gbonkonka CHP</v>
+        <v>Saahun (kpaka) MCHP</v>
       </c>
       <c r="B379" t="str">
-        <v>v2vi8UaIYlo</v>
+        <v>BG2fC2mRFOL</v>
       </c>
     </row>
     <row r="380">
@@ -5124,18 +5124,18 @@
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Yoni CHC</v>
+        <v>Mayombo MCHP</v>
       </c>
       <c r="B549" t="str">
-        <v>fAsj6a4nudH</v>
+        <v>gfk1TNPI4wN</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Mayombo MCHP</v>
+        <v>Yoni CHC</v>
       </c>
       <c r="B550" t="str">
-        <v>gfk1TNPI4wN</v>
+        <v>fAsj6a4nudH</v>
       </c>
     </row>
     <row r="551">
@@ -5404,18 +5404,18 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Madina (BUM) CHC</v>
+        <v>kamba mamudia</v>
       </c>
       <c r="B584" t="str">
-        <v>gE3gEGZbQMi</v>
+        <v>zO5hgxxfU4T</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>kamba mamudia</v>
+        <v>Madina (BUM) CHC</v>
       </c>
       <c r="B585" t="str">
-        <v>zO5hgxxfU4T</v>
+        <v>gE3gEGZbQMi</v>
       </c>
     </row>
     <row r="586">
@@ -6804,18 +6804,18 @@
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>Gbahama (Makpele) MCHP</v>
+        <v>St. Luke's Wellington</v>
       </c>
       <c r="B759" t="str">
-        <v>TWH05Rjz6oT</v>
+        <v>vxa2YQRGV7I</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>St. Luke's Wellington</v>
+        <v>Gbahama (Makpele) MCHP</v>
       </c>
       <c r="B760" t="str">
-        <v>vxa2YQRGV7I</v>
+        <v>TWH05Rjz6oT</v>
       </c>
     </row>
     <row r="761">
@@ -6956,18 +6956,18 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>Ngiehun (Lower Bambara) MCHP</v>
+        <v>Kpayama 1 MCHP</v>
       </c>
       <c r="B778" t="str">
-        <v>m21WB5iqHAb</v>
+        <v>So2b8zJfcMa</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>Kpayama 1 MCHP</v>
+        <v>Ngiehun (Lower Bambara) MCHP</v>
       </c>
       <c r="B779" t="str">
-        <v>So2b8zJfcMa</v>
+        <v>m21WB5iqHAb</v>
       </c>
     </row>
     <row r="780">
@@ -6996,18 +6996,18 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>Sandaru (Gaura) MCHP</v>
+        <v>Gbindi CHP</v>
       </c>
       <c r="B783" t="str">
-        <v>hTGeTrwzrPi</v>
+        <v>LFpl1falVZi</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>Gbindi CHP</v>
+        <v>Sandaru (Gaura) MCHP</v>
       </c>
       <c r="B784" t="str">
-        <v>LFpl1falVZi</v>
+        <v>hTGeTrwzrPi</v>
       </c>
     </row>
     <row r="785">
@@ -7044,18 +7044,18 @@
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>Torkpumbu MCHP</v>
+        <v>Mandema CHP</v>
       </c>
       <c r="B789" t="str">
-        <v>RJpiHpefEUw</v>
+        <v>WerHl8SDtRU</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>Mandema CHP</v>
+        <v>Torkpumbu MCHP</v>
       </c>
       <c r="B790" t="str">
-        <v>WerHl8SDtRU</v>
+        <v>RJpiHpefEUw</v>
       </c>
     </row>
     <row r="791">
@@ -7516,18 +7516,18 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>Sienga CHP</v>
+        <v>Needy CHC</v>
       </c>
       <c r="B848" t="str">
-        <v>a1E6QWBTEwX</v>
+        <v>UOJlcpPnBat</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>Needy CHC</v>
+        <v>Sienga CHP</v>
       </c>
       <c r="B849" t="str">
-        <v>UOJlcpPnBat</v>
+        <v>a1E6QWBTEwX</v>
       </c>
     </row>
     <row r="850">
@@ -7708,18 +7708,18 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>SLRCS (Freetown) Clinic</v>
+        <v>Konjo MCHP</v>
       </c>
       <c r="B872" t="str">
-        <v>EmTN0L4EAVi</v>
+        <v>d7hw1ababST</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>Konjo MCHP</v>
+        <v>SLRCS (Freetown) Clinic</v>
       </c>
       <c r="B873" t="str">
-        <v>d7hw1ababST</v>
+        <v>EmTN0L4EAVi</v>
       </c>
     </row>
     <row r="874">
@@ -8612,26 +8612,26 @@
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>Gloucester CHP</v>
+        <v>Mabang MCHP</v>
       </c>
       <c r="B985" t="str">
-        <v>HTDuY3uxj6u</v>
+        <v>fCFdj2T0Bq1</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>Mabang MCHP</v>
+        <v>Mano Yorgbo MCHP</v>
       </c>
       <c r="B986" t="str">
-        <v>fCFdj2T0Bq1</v>
+        <v>KvE0PYQzXMM</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>Mano Yorgbo MCHP</v>
+        <v>Gloucester CHP</v>
       </c>
       <c r="B987" t="str">
-        <v>KvE0PYQzXMM</v>
+        <v>HTDuY3uxj6u</v>
       </c>
     </row>
     <row r="988">
@@ -9140,18 +9140,18 @@
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>Rolembray MCHP</v>
+        <v>Komendeh (Nongowa) MCHP</v>
       </c>
       <c r="B1051" t="str">
-        <v>nZblzPvJ5UW</v>
+        <v>NqwvaQC1ni4</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>Komendeh (Nongowa) MCHP</v>
+        <v>Rolembray MCHP</v>
       </c>
       <c r="B1052" t="str">
-        <v>NqwvaQC1ni4</v>
+        <v>nZblzPvJ5UW</v>
       </c>
     </row>
     <row r="1053">
@@ -9516,18 +9516,18 @@
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>Tonko Maternity Clinic</v>
+        <v>Gbalan Thallan MCHP</v>
       </c>
       <c r="B1098" t="str">
-        <v>uNEhNuBUr0i</v>
+        <v>FsunWIQLXoF</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>Gbalan Thallan MCHP</v>
+        <v>Tonko Maternity Clinic</v>
       </c>
       <c r="B1099" t="str">
-        <v>FsunWIQLXoF</v>
+        <v>uNEhNuBUr0i</v>
       </c>
     </row>
     <row r="1100">
@@ -9732,18 +9732,18 @@
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>Under Fives Clinic</v>
+        <v>Mattru UBC Hospital</v>
       </c>
       <c r="B1125" t="str">
-        <v>mTNOoGXuC39</v>
+        <v>ctN0WgIvfke</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>Mattru UBC Hospital</v>
+        <v>Under Fives Clinic</v>
       </c>
       <c r="B1126" t="str">
-        <v>ctN0WgIvfke</v>
+        <v>mTNOoGXuC39</v>
       </c>
     </row>
     <row r="1127">
@@ -9804,18 +9804,18 @@
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>Lion for Lion Clinic</v>
+        <v>Gbongeima MCHP</v>
       </c>
       <c r="B1134" t="str">
-        <v>cZxP4NE5O9z</v>
+        <v>rebbn0ooFSO</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>Gbongeima MCHP</v>
+        <v>Lion for Lion Clinic</v>
       </c>
       <c r="B1135" t="str">
-        <v>rebbn0ooFSO</v>
+        <v>cZxP4NE5O9z</v>
       </c>
     </row>
     <row r="1136">
@@ -10012,18 +10012,18 @@
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>Magbeni MCHP</v>
+        <v>Kombilie MCHP</v>
       </c>
       <c r="B1160" t="str">
-        <v>UJ80rknbJtm</v>
+        <v>HC2NlwpoXfb</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>Kombilie MCHP</v>
+        <v>Magbeni MCHP</v>
       </c>
       <c r="B1161" t="str">
-        <v>HC2NlwpoXfb</v>
+        <v>UJ80rknbJtm</v>
       </c>
     </row>
     <row r="1162">

--- a/test-harness/.tmp/aggregate-filled.xlsx
+++ b/test-harness/.tmp/aggregate-filled.xlsx
@@ -418,7 +418,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Generated: 2026-04-23T13:18:37.556Z</v>
+        <v>Generated: 2026-04-23T14:27:58.163Z</v>
       </c>
     </row>
     <row r="6">
@@ -772,18 +772,18 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Matoto MCHP</v>
+        <v>Masselleh MCHP</v>
       </c>
       <c r="B5" t="str">
-        <v>uGa5JtIMfRx</v>
+        <v>cag6vQQ9SQk</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Masselleh MCHP</v>
+        <v>Matoto MCHP</v>
       </c>
       <c r="B6" t="str">
-        <v>cag6vQQ9SQk</v>
+        <v>uGa5JtIMfRx</v>
       </c>
     </row>
     <row r="7">
@@ -1140,18 +1140,18 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Timbo CHP</v>
+        <v>SLRC (Mattru) Clinic</v>
       </c>
       <c r="B51" t="str">
-        <v>svCLFkT99Yx</v>
+        <v>T2Cn45nBY0u</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SLRC (Mattru) Clinic</v>
+        <v>Timbo CHP</v>
       </c>
       <c r="B52" t="str">
-        <v>T2Cn45nBY0u</v>
+        <v>svCLFkT99Yx</v>
       </c>
     </row>
     <row r="53">
@@ -1180,18 +1180,18 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Banana Island MCHP</v>
+        <v>Rofutha MCHP</v>
       </c>
       <c r="B56" t="str">
-        <v>jjtzkzrmG7s</v>
+        <v>G5FuODAbH6X</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Rofutha MCHP</v>
+        <v>Banana Island MCHP</v>
       </c>
       <c r="B57" t="str">
-        <v>G5FuODAbH6X</v>
+        <v>jjtzkzrmG7s</v>
       </c>
     </row>
     <row r="58">
@@ -1372,18 +1372,18 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Nekabo CHC</v>
+        <v>Kissy Town CHP</v>
       </c>
       <c r="B80" t="str">
-        <v>L4Tw4NlaMjn</v>
+        <v>lmNWdmeOYmV</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Kissy Town CHP</v>
+        <v>Nekabo CHC</v>
       </c>
       <c r="B81" t="str">
-        <v>lmNWdmeOYmV</v>
+        <v>L4Tw4NlaMjn</v>
       </c>
     </row>
     <row r="82">
@@ -1612,18 +1612,18 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Stella Maries Clinic</v>
+        <v>Yemoh Town CHC</v>
       </c>
       <c r="B110" t="str">
-        <v>Ea3j0kUvyWg</v>
+        <v>RhJbg8UD75Q</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Yemoh Town CHC</v>
+        <v>Stella Maries Clinic</v>
       </c>
       <c r="B111" t="str">
-        <v>RhJbg8UD75Q</v>
+        <v>Ea3j0kUvyWg</v>
       </c>
     </row>
     <row r="112">
@@ -1676,18 +1676,18 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Minah MCHP</v>
+        <v>Mogbasske CHP</v>
       </c>
       <c r="B118" t="str">
-        <v>ZW3XCXXiLcO</v>
+        <v>DZaJmtlaBMl</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Mogbasske CHP</v>
+        <v>Minah MCHP</v>
       </c>
       <c r="B119" t="str">
-        <v>DZaJmtlaBMl</v>
+        <v>ZW3XCXXiLcO</v>
       </c>
     </row>
     <row r="120">
@@ -1796,26 +1796,26 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Kaponkie MCHP</v>
+        <v>Woyama MCHP</v>
       </c>
       <c r="B133" t="str">
-        <v>Crgx572DnXR</v>
+        <v>fPe1l06MurL</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Woyama MCHP</v>
+        <v>Mabora MCHP</v>
       </c>
       <c r="B134" t="str">
-        <v>fPe1l06MurL</v>
+        <v>fmkqsEx6MRo</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Mabora MCHP</v>
+        <v>Kaponkie MCHP</v>
       </c>
       <c r="B135" t="str">
-        <v>fmkqsEx6MRo</v>
+        <v>Crgx572DnXR</v>
       </c>
     </row>
     <row r="136">
@@ -1852,18 +1852,18 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Masankoro MCHP</v>
+        <v>Small Sefadu MCHP</v>
       </c>
       <c r="B140" t="str">
-        <v>l3jnkNNpoD8</v>
+        <v>ncGs9vXS36w</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Small Sefadu MCHP</v>
+        <v>Masankoro MCHP</v>
       </c>
       <c r="B141" t="str">
-        <v>ncGs9vXS36w</v>
+        <v>l3jnkNNpoD8</v>
       </c>
     </row>
     <row r="142">
@@ -1924,18 +1924,18 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Scan Drive MCHP</v>
+        <v>Kokoru CHP</v>
       </c>
       <c r="B149" t="str">
-        <v>u1eQDDtKqm7</v>
+        <v>F2TAF765q1b</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Kokoru CHP</v>
+        <v>Scan Drive MCHP</v>
       </c>
       <c r="B150" t="str">
-        <v>F2TAF765q1b</v>
+        <v>u1eQDDtKqm7</v>
       </c>
     </row>
     <row r="151">
@@ -1980,18 +1980,18 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Bambawolo CHP</v>
+        <v>Madina (Malema) MCHP</v>
       </c>
       <c r="B156" t="str">
-        <v>TNbHYOuQi8s</v>
+        <v>SFQigiC2ISS</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Madina (Malema) MCHP</v>
+        <v>Bambawolo CHP</v>
       </c>
       <c r="B157" t="str">
-        <v>SFQigiC2ISS</v>
+        <v>TNbHYOuQi8s</v>
       </c>
     </row>
     <row r="158">
@@ -2140,18 +2140,18 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Masongbo CHC</v>
+        <v>Mabineh MCHP</v>
       </c>
       <c r="B176" t="str">
-        <v>uRQj8WRK0Py</v>
+        <v>mc3jvzpzSi4</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Mabineh MCHP</v>
+        <v>Masongbo CHC</v>
       </c>
       <c r="B177" t="str">
-        <v>mc3jvzpzSi4</v>
+        <v>uRQj8WRK0Py</v>
       </c>
     </row>
     <row r="178">
@@ -2356,18 +2356,18 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Masumbrie MCHP</v>
+        <v>Worreh MCHP</v>
       </c>
       <c r="B203" t="str">
-        <v>flJbtXOQ4ha</v>
+        <v>VSwnkMSAdp7</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Worreh MCHP</v>
+        <v>Masumbrie MCHP</v>
       </c>
       <c r="B204" t="str">
-        <v>VSwnkMSAdp7</v>
+        <v>flJbtXOQ4ha</v>
       </c>
     </row>
     <row r="205">
@@ -2444,18 +2444,18 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Mamanso Kafla MCHP</v>
+        <v>Kindoyal Hospital</v>
       </c>
       <c r="B214" t="str">
-        <v>T1lTKu6zkHN</v>
+        <v>uROAmk9ymNE</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Kindoyal Hospital</v>
+        <v>Mamanso Kafla MCHP</v>
       </c>
       <c r="B215" t="str">
-        <v>uROAmk9ymNE</v>
+        <v>T1lTKu6zkHN</v>
       </c>
     </row>
     <row r="216">
@@ -2524,26 +2524,26 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Kanekor MCHP</v>
+        <v>Magbassabana MCHP</v>
       </c>
       <c r="B224" t="str">
-        <v>tXL6C7P0ObJ</v>
+        <v>bf6PXrSNMKK</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Bumpeh River CHP</v>
+        <v>Kanekor MCHP</v>
       </c>
       <c r="B225" t="str">
-        <v>mkIugjeYSjE</v>
+        <v>tXL6C7P0ObJ</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Magbassabana MCHP</v>
+        <v>Bumpeh River CHP</v>
       </c>
       <c r="B226" t="str">
-        <v>bf6PXrSNMKK</v>
+        <v>mkIugjeYSjE</v>
       </c>
     </row>
     <row r="227">
@@ -2612,18 +2612,18 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Delken MCHP</v>
+        <v>Jangalor MCHP</v>
       </c>
       <c r="B235" t="str">
-        <v>sSgOnY1Xqd9</v>
+        <v>qzm5ww3U0vz</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Jangalor MCHP</v>
+        <v>Delken MCHP</v>
       </c>
       <c r="B236" t="str">
-        <v>qzm5ww3U0vz</v>
+        <v>sSgOnY1Xqd9</v>
       </c>
     </row>
     <row r="237">
@@ -2956,18 +2956,18 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Numea CHC</v>
+        <v>Tongoro MCHP</v>
       </c>
       <c r="B278" t="str">
-        <v>PduUQmdt0pB</v>
+        <v>iIpPPnnzDo6</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Tongoro MCHP</v>
+        <v>Numea CHC</v>
       </c>
       <c r="B279" t="str">
-        <v>iIpPPnnzDo6</v>
+        <v>PduUQmdt0pB</v>
       </c>
     </row>
     <row r="280">
@@ -3052,34 +3052,34 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Senjekoro MCHP</v>
+        <v>Bo Govt. Hosp.</v>
       </c>
       <c r="B290" t="str">
-        <v>tcEjL7gmFJL</v>
+        <v>rZxk3S0qN63</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Bo Govt. Hosp.</v>
+        <v>Senjekoro MCHP</v>
       </c>
       <c r="B291" t="str">
-        <v>rZxk3S0qN63</v>
+        <v>tcEjL7gmFJL</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>UFC Bonthe</v>
+        <v>Tonkomba MCHP</v>
       </c>
       <c r="B292" t="str">
-        <v>gGv9ATEs68L</v>
+        <v>xIMxph4NMP1</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Tonkomba MCHP</v>
+        <v>UFC Bonthe</v>
       </c>
       <c r="B293" t="str">
-        <v>xIMxph4NMP1</v>
+        <v>gGv9ATEs68L</v>
       </c>
     </row>
     <row r="294">
@@ -3172,18 +3172,18 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Mercy Ship ACFC</v>
+        <v>Fatibra CHP</v>
       </c>
       <c r="B305" t="str">
-        <v>xO9WbCvFq5k</v>
+        <v>jfV49JGnYKF</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Fatibra CHP</v>
+        <v>Mercy Ship ACFC</v>
       </c>
       <c r="B306" t="str">
-        <v>jfV49JGnYKF</v>
+        <v>xO9WbCvFq5k</v>
       </c>
     </row>
     <row r="307">
@@ -3420,18 +3420,18 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Makobeh MCHP</v>
+        <v>Yataya CHP</v>
       </c>
       <c r="B336" t="str">
-        <v>iMDr2FG7i8Q</v>
+        <v>MErVkzdbsP5</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Yataya CHP</v>
+        <v>Makobeh MCHP</v>
       </c>
       <c r="B337" t="str">
-        <v>MErVkzdbsP5</v>
+        <v>iMDr2FG7i8Q</v>
       </c>
     </row>
     <row r="338">
@@ -3444,18 +3444,18 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Mabayo MCHP</v>
+        <v>Dankawalie MCHP</v>
       </c>
       <c r="B339" t="str">
-        <v>Xzxy8NuVsLp</v>
+        <v>DErmFP7bri7</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Dankawalie MCHP</v>
+        <v>Mabayo MCHP</v>
       </c>
       <c r="B340" t="str">
-        <v>DErmFP7bri7</v>
+        <v>Xzxy8NuVsLp</v>
       </c>
     </row>
     <row r="341">
@@ -3516,18 +3516,18 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Masamboi MCHP</v>
+        <v>Gbetema MCHP (Fiama)</v>
       </c>
       <c r="B348" t="str">
-        <v>Hu31NCRjZlj</v>
+        <v>as1dnmlXLzG</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gbetema MCHP (Fiama)</v>
+        <v>Masamboi MCHP</v>
       </c>
       <c r="B349" t="str">
-        <v>as1dnmlXLzG</v>
+        <v>Hu31NCRjZlj</v>
       </c>
     </row>
     <row r="350">
@@ -4356,18 +4356,18 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Kpetema MCHP</v>
+        <v>Ngueh MCHP</v>
       </c>
       <c r="B453" t="str">
-        <v>kDxbU1uSBFh</v>
+        <v>Vw4Uv6UPIPC</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Ngueh MCHP</v>
+        <v>Kpetema MCHP</v>
       </c>
       <c r="B454" t="str">
-        <v>Vw4Uv6UPIPC</v>
+        <v>kDxbU1uSBFh</v>
       </c>
     </row>
     <row r="455">
@@ -4516,18 +4516,18 @@
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Praise Foundation CHC</v>
+        <v>Mayassoh MCHP</v>
       </c>
       <c r="B473" t="str">
-        <v>wtdBuXDwZYQ</v>
+        <v>Z8Cm76B2726</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Mayassoh MCHP</v>
+        <v>Praise Foundation CHC</v>
       </c>
       <c r="B474" t="str">
-        <v>Z8Cm76B2726</v>
+        <v>wtdBuXDwZYQ</v>
       </c>
     </row>
     <row r="475">
@@ -4804,18 +4804,18 @@
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Rosint Buya MCHP</v>
+        <v>Sahn Bumpe MCHP</v>
       </c>
       <c r="B509" t="str">
-        <v>el8sgzyHuEe</v>
+        <v>NDqR2cWlVy3</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Sahn Bumpe MCHP</v>
+        <v>Rosint Buya MCHP</v>
       </c>
       <c r="B510" t="str">
-        <v>NDqR2cWlVy3</v>
+        <v>el8sgzyHuEe</v>
       </c>
     </row>
     <row r="511">
@@ -5004,18 +5004,18 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Gbangba MCHP</v>
+        <v>Wai MCHP</v>
       </c>
       <c r="B534" t="str">
-        <v>r93q83kZoR9</v>
+        <v>zCSWBz2pyMd</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Wai MCHP</v>
+        <v>Gbangba MCHP</v>
       </c>
       <c r="B535" t="str">
-        <v>zCSWBz2pyMd</v>
+        <v>r93q83kZoR9</v>
       </c>
     </row>
     <row r="536">
@@ -5404,18 +5404,18 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>kamba mamudia</v>
+        <v>Madina (BUM) CHC</v>
       </c>
       <c r="B584" t="str">
-        <v>zO5hgxxfU4T</v>
+        <v>gE3gEGZbQMi</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Madina (BUM) CHC</v>
+        <v>kamba mamudia</v>
       </c>
       <c r="B585" t="str">
-        <v>gE3gEGZbQMi</v>
+        <v>zO5hgxxfU4T</v>
       </c>
     </row>
     <row r="586">
@@ -5564,18 +5564,18 @@
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Gbendembu Wesleyan CHC</v>
+        <v>Bandasuma Fiama MCHP</v>
       </c>
       <c r="B604" t="str">
-        <v>YAuJ3fyoEuI</v>
+        <v>aF6iPGbrcRk</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Bandasuma Fiama MCHP</v>
+        <v>Gbendembu Wesleyan CHC</v>
       </c>
       <c r="B605" t="str">
-        <v>aF6iPGbrcRk</v>
+        <v>YAuJ3fyoEuI</v>
       </c>
     </row>
     <row r="606">
@@ -5764,18 +5764,18 @@
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Wordu CHP</v>
+        <v>Robat MCHP</v>
       </c>
       <c r="B629" t="str">
-        <v>bW5BaqrBM4K</v>
+        <v>gP6hn503KUX</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Robat MCHP</v>
+        <v>Wordu CHP</v>
       </c>
       <c r="B630" t="str">
-        <v>gP6hn503KUX</v>
+        <v>bW5BaqrBM4K</v>
       </c>
     </row>
     <row r="631">
@@ -5796,18 +5796,18 @@
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>SLRCS (Nongowa) clinic</v>
+        <v>Wellbody MCHP</v>
       </c>
       <c r="B633" t="str">
-        <v>Vnc2qIRLbyw</v>
+        <v>XuGfiry96Bg</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Wellbody MCHP</v>
+        <v>SLRCS (Nongowa) clinic</v>
       </c>
       <c r="B634" t="str">
-        <v>XuGfiry96Bg</v>
+        <v>Vnc2qIRLbyw</v>
       </c>
     </row>
     <row r="635">
@@ -5860,18 +5860,18 @@
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Bendu Mameima CHC</v>
+        <v>Kamba MCHP</v>
       </c>
       <c r="B641" t="str">
-        <v>amgb83zVxp5</v>
+        <v>cJ7omISg7gG</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Kamba MCHP</v>
+        <v>Bendu Mameima CHC</v>
       </c>
       <c r="B642" t="str">
-        <v>cJ7omISg7gG</v>
+        <v>amgb83zVxp5</v>
       </c>
     </row>
     <row r="643">
@@ -6572,18 +6572,18 @@
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>Kania (Masungbala) MCHP</v>
+        <v>Musaia CHP</v>
       </c>
       <c r="B730" t="str">
-        <v>RNGpZqutw3Y</v>
+        <v>sTOXJA2KcY2</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>Musaia CHP</v>
+        <v>Kania (Masungbala) MCHP</v>
       </c>
       <c r="B731" t="str">
-        <v>sTOXJA2KcY2</v>
+        <v>RNGpZqutw3Y</v>
       </c>
     </row>
     <row r="732">
@@ -6684,18 +6684,18 @@
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>Koakor MCHP</v>
+        <v>Sumbuya CHC</v>
       </c>
       <c r="B744" t="str">
-        <v>EQc3n1juPFn</v>
+        <v>W2KnxOMvmgE</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>Sumbuya CHC</v>
+        <v>Koakor MCHP</v>
       </c>
       <c r="B745" t="str">
-        <v>W2KnxOMvmgE</v>
+        <v>EQc3n1juPFn</v>
       </c>
     </row>
     <row r="746">
@@ -6916,18 +6916,18 @@
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>Gissiwolo MCHP</v>
+        <v>Rothatha MCHP</v>
       </c>
       <c r="B773" t="str">
-        <v>AekX8HBymng</v>
+        <v>KaevAHPgkA8</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>Rothatha MCHP</v>
+        <v>Gissiwolo MCHP</v>
       </c>
       <c r="B774" t="str">
-        <v>KaevAHPgkA8</v>
+        <v>AekX8HBymng</v>
       </c>
     </row>
     <row r="775">
@@ -6940,50 +6940,50 @@
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>Sebengu MCHP</v>
+        <v>Sengama MCHP</v>
       </c>
       <c r="B776" t="str">
-        <v>Jd7G0NYBTx1</v>
+        <v>MBtmOhLs7y1</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>Sengama MCHP</v>
+        <v>Sebengu MCHP</v>
       </c>
       <c r="B777" t="str">
-        <v>MBtmOhLs7y1</v>
+        <v>Jd7G0NYBTx1</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>Kpayama 1 MCHP</v>
+        <v>Ngiehun (Lower Bambara) MCHP</v>
       </c>
       <c r="B778" t="str">
-        <v>So2b8zJfcMa</v>
+        <v>m21WB5iqHAb</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>Ngiehun (Lower Bambara) MCHP</v>
+        <v>Kpayama 1 MCHP</v>
       </c>
       <c r="B779" t="str">
-        <v>m21WB5iqHAb</v>
+        <v>So2b8zJfcMa</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>Gbandiwulo CHP</v>
+        <v>Manewa MCHP</v>
       </c>
       <c r="B780" t="str">
-        <v>Vw6CNyFUeh9</v>
+        <v>CTnuuI55SOj</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>Manewa MCHP</v>
+        <v>Gbandiwulo CHP</v>
       </c>
       <c r="B781" t="str">
-        <v>CTnuuI55SOj</v>
+        <v>Vw6CNyFUeh9</v>
       </c>
     </row>
     <row r="782">
@@ -6996,18 +6996,18 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>Gbindi CHP</v>
+        <v>Sandaru (Gaura) MCHP</v>
       </c>
       <c r="B783" t="str">
-        <v>LFpl1falVZi</v>
+        <v>hTGeTrwzrPi</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>Sandaru (Gaura) MCHP</v>
+        <v>Gbindi CHP</v>
       </c>
       <c r="B784" t="str">
-        <v>hTGeTrwzrPi</v>
+        <v>LFpl1falVZi</v>
       </c>
     </row>
     <row r="785">
@@ -7044,18 +7044,18 @@
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>Mandema CHP</v>
+        <v>Torkpumbu MCHP</v>
       </c>
       <c r="B789" t="str">
-        <v>WerHl8SDtRU</v>
+        <v>RJpiHpefEUw</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>Torkpumbu MCHP</v>
+        <v>Mandema CHP</v>
       </c>
       <c r="B790" t="str">
-        <v>RJpiHpefEUw</v>
+        <v>WerHl8SDtRU</v>
       </c>
     </row>
     <row r="791">
@@ -7516,26 +7516,26 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>Needy CHC</v>
+        <v>Sienga CHP</v>
       </c>
       <c r="B848" t="str">
-        <v>UOJlcpPnBat</v>
+        <v>a1E6QWBTEwX</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>Sienga CHP</v>
+        <v>Needy CHC</v>
       </c>
       <c r="B849" t="str">
-        <v>a1E6QWBTEwX</v>
+        <v>UOJlcpPnBat</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>Mayakie MCHP</v>
+        <v>New Maforkie CHP</v>
       </c>
       <c r="B850" t="str">
-        <v>R0CmUlFULXg</v>
+        <v>lzz1UhTzO4E</v>
       </c>
     </row>
     <row r="851">
@@ -7548,10 +7548,10 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>New Maforkie CHP</v>
+        <v>Mayakie MCHP</v>
       </c>
       <c r="B852" t="str">
-        <v>lzz1UhTzO4E</v>
+        <v>R0CmUlFULXg</v>
       </c>
     </row>
     <row r="853">
@@ -7684,18 +7684,18 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>Njama MCHP</v>
+        <v>Bongor MCHP</v>
       </c>
       <c r="B869" t="str">
-        <v>WMj6mBDw76A</v>
+        <v>zAyK28LLaez</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>Bongor MCHP</v>
+        <v>Njama MCHP</v>
       </c>
       <c r="B870" t="str">
-        <v>zAyK28LLaez</v>
+        <v>WMj6mBDw76A</v>
       </c>
     </row>
     <row r="871">
@@ -7708,18 +7708,18 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>Konjo MCHP</v>
+        <v>SLRCS (Freetown) Clinic</v>
       </c>
       <c r="B872" t="str">
-        <v>d7hw1ababST</v>
+        <v>EmTN0L4EAVi</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>SLRCS (Freetown) Clinic</v>
+        <v>Konjo MCHP</v>
       </c>
       <c r="B873" t="str">
-        <v>EmTN0L4EAVi</v>
+        <v>d7hw1ababST</v>
       </c>
     </row>
     <row r="874">
@@ -7804,18 +7804,18 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>Kambama CHP</v>
+        <v>Sandayeima MCHP</v>
       </c>
       <c r="B884" t="str">
-        <v>mYMJHVqdBKt</v>
+        <v>oUR5HPmim7E</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>Sandayeima MCHP</v>
+        <v>Kambama CHP</v>
       </c>
       <c r="B885" t="str">
-        <v>oUR5HPmim7E</v>
+        <v>mYMJHVqdBKt</v>
       </c>
     </row>
     <row r="886">
@@ -8212,18 +8212,18 @@
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>Mende Buima MCHP</v>
+        <v>Tissana MCHP</v>
       </c>
       <c r="B935" t="str">
-        <v>NnGUNkc5Zq8</v>
+        <v>SptGAcmbgPz</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>Tissana MCHP</v>
+        <v>Mende Buima MCHP</v>
       </c>
       <c r="B936" t="str">
-        <v>SptGAcmbgPz</v>
+        <v>NnGUNkc5Zq8</v>
       </c>
     </row>
     <row r="937">
@@ -8516,18 +8516,18 @@
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>Kondeya (Sandor) MCHP</v>
+        <v>Mokorbu MCHP</v>
       </c>
       <c r="B973" t="str">
-        <v>e5sGsWLEn3k</v>
+        <v>cHqboEGRUiY</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>Mokorbu MCHP</v>
+        <v>Kondeya (Sandor) MCHP</v>
       </c>
       <c r="B974" t="str">
-        <v>cHqboEGRUiY</v>
+        <v>e5sGsWLEn3k</v>
       </c>
     </row>
     <row r="975">
@@ -8612,26 +8612,26 @@
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>Mabang MCHP</v>
+        <v>Mano Yorgbo MCHP</v>
       </c>
       <c r="B985" t="str">
-        <v>fCFdj2T0Bq1</v>
+        <v>KvE0PYQzXMM</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>Mano Yorgbo MCHP</v>
+        <v>Gloucester CHP</v>
       </c>
       <c r="B986" t="str">
-        <v>KvE0PYQzXMM</v>
+        <v>HTDuY3uxj6u</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>Gloucester CHP</v>
+        <v>Mabang MCHP</v>
       </c>
       <c r="B987" t="str">
-        <v>HTDuY3uxj6u</v>
+        <v>fCFdj2T0Bq1</v>
       </c>
     </row>
     <row r="988">
@@ -8924,18 +8924,18 @@
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>Laleihun Kovoma CHC</v>
+        <v>Sumbaria MCHP</v>
       </c>
       <c r="B1024" t="str">
-        <v>N3tpEjZcPm9</v>
+        <v>GvstqlRRnpV</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>Sumbaria MCHP</v>
+        <v>Laleihun Kovoma CHC</v>
       </c>
       <c r="B1025" t="str">
-        <v>GvstqlRRnpV</v>
+        <v>N3tpEjZcPm9</v>
       </c>
     </row>
     <row r="1026">
@@ -9060,10 +9060,10 @@
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>Mosanda CHP</v>
+        <v>Pewama CHP</v>
       </c>
       <c r="B1041" t="str">
-        <v>cDRQOxX1wHO</v>
+        <v>nbMpoRiVRWd</v>
       </c>
     </row>
     <row r="1042">
@@ -9076,10 +9076,10 @@
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>Pewama CHP</v>
+        <v>Mosanda CHP</v>
       </c>
       <c r="B1043" t="str">
-        <v>nbMpoRiVRWd</v>
+        <v>cDRQOxX1wHO</v>
       </c>
     </row>
     <row r="1044">
@@ -9140,18 +9140,18 @@
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>Komendeh (Nongowa) MCHP</v>
+        <v>Rolembray MCHP</v>
       </c>
       <c r="B1051" t="str">
-        <v>NqwvaQC1ni4</v>
+        <v>nZblzPvJ5UW</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>Rolembray MCHP</v>
+        <v>Komendeh (Nongowa) MCHP</v>
       </c>
       <c r="B1052" t="str">
-        <v>nZblzPvJ5UW</v>
+        <v>NqwvaQC1ni4</v>
       </c>
     </row>
     <row r="1053">
@@ -9228,18 +9228,18 @@
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>Yele CHC</v>
+        <v>Mabolleh MCHP</v>
       </c>
       <c r="B1062" t="str">
-        <v>sesv0eXljBq</v>
+        <v>PybxeRWVSrI</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>Mabolleh MCHP</v>
+        <v>Yele CHC</v>
       </c>
       <c r="B1063" t="str">
-        <v>PybxeRWVSrI</v>
+        <v>sesv0eXljBq</v>
       </c>
     </row>
     <row r="1064">
@@ -9516,18 +9516,18 @@
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>Gbalan Thallan MCHP</v>
+        <v>Tonko Maternity Clinic</v>
       </c>
       <c r="B1098" t="str">
-        <v>FsunWIQLXoF</v>
+        <v>uNEhNuBUr0i</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>Tonko Maternity Clinic</v>
+        <v>Gbalan Thallan MCHP</v>
       </c>
       <c r="B1099" t="str">
-        <v>uNEhNuBUr0i</v>
+        <v>FsunWIQLXoF</v>
       </c>
     </row>
     <row r="1100">
@@ -9644,18 +9644,18 @@
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>Bumban MCHP</v>
+        <v>Tagrin CHC</v>
       </c>
       <c r="B1114" t="str">
-        <v>OI0BQUurVFS</v>
+        <v>O63vIA5MVn6</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>Tagrin CHC</v>
+        <v>Bumban MCHP</v>
       </c>
       <c r="B1115" t="str">
-        <v>O63vIA5MVn6</v>
+        <v>OI0BQUurVFS</v>
       </c>
     </row>
     <row r="1116">
@@ -9804,18 +9804,18 @@
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>Gbongeima MCHP</v>
+        <v>Lion for Lion Clinic</v>
       </c>
       <c r="B1134" t="str">
-        <v>rebbn0ooFSO</v>
+        <v>cZxP4NE5O9z</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>Lion for Lion Clinic</v>
+        <v>Gbongeima MCHP</v>
       </c>
       <c r="B1135" t="str">
-        <v>cZxP4NE5O9z</v>
+        <v>rebbn0ooFSO</v>
       </c>
     </row>
     <row r="1136">
@@ -10052,18 +10052,18 @@
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>Mabang CHC</v>
+        <v>Gbonkobana CHP</v>
       </c>
       <c r="B1165" t="str">
-        <v>Ahh47q8AkId</v>
+        <v>BXJnMD2eJAx</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>Gbonkobana CHP</v>
+        <v>Mabang CHC</v>
       </c>
       <c r="B1166" t="str">
-        <v>BXJnMD2eJAx</v>
+        <v>Ahh47q8AkId</v>
       </c>
     </row>
     <row r="1167">
